--- a/catalogo_operaciones.xlsx
+++ b/catalogo_operaciones.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Operaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Operaciones'!$A$1:$D$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Operaciones'!$A$1:$D$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -142,7 +142,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OperationsCatalog" displayName="OperationsCatalog" ref="A1:D65" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OperationsCatalog" displayName="OperationsCatalog" ref="A1:D71" headerRowCount="1">
   <autoFilter ref="A1:D65"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Nombre exacto de la función"/>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1882,8 +1882,140 @@
         </is>
       </c>
     </row>
+    <row r="66" ht="42" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>contains</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>TextProcessor</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, search_text: str, create_new_column: bool = False, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Devuelve True si el texto de cada celda contiene literalmente search_text; en caso contrario False. Los nulos producen False.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="42" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>starts_with</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>TextProcessor</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, search_text: str, create_new_column: bool = False, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Devuelve True si el texto de cada celda comienza literalmente con search_text; en caso contrario False. Los nulos producen False.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="42" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>ends_with</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>TextProcessor</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, search_text: str, create_new_column: bool = False, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Devuelve True si el texto de cada celda termina literalmente con search_text; en caso contrario False. Los nulos producen False.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="42" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>transform_left</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>TextProcessor</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, limit: int, create_new_column: bool = False, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Conserva como máximo los primeros limit caracteres de cada valor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="42" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>transform_right</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>TextProcessor</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, limit: int, create_new_column: bool = False, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Conserva como máximo los últimos limit caracteres de cada valor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="42" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>TextProcessor</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Calcula la longitud en caracteres de cada celda; los valores nulos se mantienen nulos.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D65"/>
+  <autoFilter ref="A1:D71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/catalogo_operaciones.xlsx
+++ b/catalogo_operaciones.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Operaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Operaciones'!$A$1:$D$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Operaciones'!$A$1:$D$73</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -142,7 +142,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OperationsCatalog" displayName="OperationsCatalog" ref="A1:D71" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OperationsCatalog" displayName="OperationsCatalog" ref="A1:D73" headerRowCount="1">
   <autoFilter ref="A1:D65"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Nombre exacto de la función"/>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2014,8 +2014,52 @@
         </is>
       </c>
     </row>
+    <row r="72" ht="42" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>proper</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>TextProcessor</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Convierte la primera letra de cada palabra a mayúscula y el resto a minúscula; puede reemplazar la columna o crear una nueva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="42" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>propper</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>TextProcessor</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Alias de proper: convierte la primera letra de cada palabra a mayúscula y el resto a minúscula; puede reemplazar la columna o crear una nueva.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D71"/>
+  <autoFilter ref="A1:D73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/catalogo_operaciones.xlsx
+++ b/catalogo_operaciones.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Operaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Operaciones'!$A$1:$D$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Operaciones'!$A$1:$D$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -142,7 +142,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OperationsCatalog" displayName="OperationsCatalog" ref="A1:D73" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OperationsCatalog" displayName="OperationsCatalog" ref="A1:D99" headerRowCount="1">
   <autoFilter ref="A1:D65"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Nombre exacto de la función"/>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, unit: str, amount: int, create_new_column: bool = False, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, unit: str | None = None, amount: int | None = None, create_new_column: bool = False, new_column_name: str | None = None, *, part: str | None = None, interval: int | None = None, replace: bool | None = None</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Suma una cantidad de días, meses o años a una columna de fechas.</t>
+          <t>Agrega un intervalo entero de días, semanas, meses, trimestres, años, horas, minutos o segundos a una fecha. Acepta unit/amount o part/interval y reemplazo opcional.</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, start_column: str, end_column: str, unit: str = 'days', create_new_column: bool = False, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, start_column: str, end_column: str, unit: str = 'days', create_new_column: bool = False, new_column_name: str | None = None, *, part: str | None = None</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Calcula la diferencia entre dos columnas de fechas en días, meses o años completos.</t>
+          <t>Calcula la diferencia entre dos fechas en la unidad indicada: días, semanas, meses, trimestres, años, horas, minutos o segundos. Meses, trimestres y años cuentan unidades calendario completas.</t>
         </is>
       </c>
     </row>
@@ -2058,8 +2058,488 @@
         </is>
       </c>
     </row>
+    <row r="74" ht="42" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>date_parse</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, date_format: str, replace: bool = True, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Convierte usando el formato indicado; los valores inválidos se convierten a NaT. Puede reemplazar o crear columna.</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n"/>
+    </row>
+    <row r="75" ht="42" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>dateparse</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, date_format: str, replace: bool = True, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Alias normalizado de date_parse; los valores inválidos se convierten a NaT.</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n"/>
+    </row>
+    <row r="76" ht="42" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>date_trunc</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, part: str, replace: bool = True, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Trunca la fecha al inicio de año, trimestre, mes, semana (lunes), día, hora, minuto o segundo.</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n"/>
+    </row>
+    <row r="77" ht="42" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>datetrunc</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, part: str, replace: bool = True, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Alias normalizado de date_trunc.</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n"/>
+    </row>
+    <row r="78" ht="42" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Extrae el día del mes como entero.</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n"/>
+    </row>
+    <row r="79" ht="42" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>iso_quarter</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Calcula el trimestre basado en semanas ISO; la semana 53 pertenece al trimestre 4.</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n"/>
+    </row>
+    <row r="80" ht="42" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>isoquarter</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Alias normalizado de iso_quarter.</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n"/>
+    </row>
+    <row r="81" ht="42" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>iso_week</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Extrae el número de semana ISO 8601 como entero.</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n"/>
+    </row>
+    <row r="82" ht="42" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>isoweek</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Alias normalizado de iso_week.</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n"/>
+    </row>
+    <row r="83" ht="42" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>iso_week_day</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Extrae el día de la semana ISO 8601: lunes=1 hasta domingo=7.</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n"/>
+    </row>
+    <row r="84" ht="42" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>isoweekday</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Alias normalizado de iso_week_day.</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n"/>
+    </row>
+    <row r="85" ht="42" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>iso_year</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Extrae el año ISO 8601, que puede diferir del año calendario.</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n"/>
+    </row>
+    <row r="86" ht="42" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>isoyear</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Alias normalizado de iso_year.</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n"/>
+    </row>
+    <row r="87" ht="42" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>now</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Asigna la fecha y hora local actual del sistema a la columna destino.</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n"/>
+    </row>
+    <row r="88" ht="42" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>quarter</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Extrae el trimestre calendario como entero entre 1 y 4.</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n"/>
+    </row>
+    <row r="89" ht="42" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Asigna la fecha local actual del sistema sin hora a la columna destino.</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n"/>
+    </row>
+    <row r="90" ht="42" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>week</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Extrae el día de la semana como entero, lunes=0 hasta domingo=6.</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n"/>
+    </row>
+    <row r="91" ht="42" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Extrae el año calendario como entero.</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n"/>
+    </row>
+    <row r="92" ht="42" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>dateadd</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, unit: str | None = None, amount: int | None = None, create_new_column: bool = False, new_column_name: str | None = None, *, part: str | None = None, interval: int | None = None, replace: bool | None = None</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Alias normalizado de date_add.</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n"/>
+    </row>
+    <row r="93" ht="42" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>datediff</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, start_column: str, end_column: str, unit: str = 'days', create_new_column: bool = False, new_column_name: str | None = None, *, part: str | None = None</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Alias normalizado de date_diff.</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n"/>
+    </row>
+    <row r="94" ht="42" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>date_name</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, part: str, replace: bool = True, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Devuelve el nombre en español del mes o del día de semana; año y trimestre se devuelven como texto.</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n"/>
+    </row>
+    <row r="95" ht="42" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>datename</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, part: str, replace: bool = True, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Alias normalizado de date_name.</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n"/>
+    </row>
+    <row r="96" ht="42" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Extrae el número del mes como entero entre 1 y 12.</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n"/>
+    </row>
+    <row r="97" ht="42" customHeight="1">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>date add</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, unit: str | None = None, amount: int | None = None, create_new_column: bool = False, new_column_name: str | None = None, *, part: str | None = None, interval: int | None = None, replace: bool | None = None</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Alias textual de date_add.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="42" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>date diff</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, start_column: str, end_column: str, unit: str = 'days', create_new_column: bool = False, new_column_name: str | None = None, *, part: str | None = None</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Alias textual de date_diff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="42" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>date name</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, part: str, replace: bool = True, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Alias textual de date_name.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D73"/>
+  <autoFilter ref="A1:D99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/catalogo_operaciones.xlsx
+++ b/catalogo_operaciones.xlsx
@@ -2,16 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Operaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Operaciones'!$A$1:$D$99</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,8 +25,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FFffffff"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -41,11 +46,33 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="FF1f4e78"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFc6c6c6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFc6c6c6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFc6c6c6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFc6c6c6"/>
+      </bottom>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -55,19 +82,25 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="general" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -142,15 +175,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OperationsCatalog" displayName="OperationsCatalog" ref="A1:D99" headerRowCount="1">
-  <autoFilter ref="A1:D65"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OperationsCatalog" displayName="OperationsCatalog" ref="A1:D99" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A1:D99"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Nombre exacto de la función"/>
     <tableColumn id="2" name="Nombre de su clase"/>
     <tableColumn id="3" name="Parámetros de entrada"/>
     <tableColumn id="4" name="Descripción"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -159,10 +192,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -200,69 +233,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -286,54 +321,53 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="15000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
+                <a:tint val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
+              <a:shade val="9500"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -343,7 +377,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -352,7 +386,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -361,7 +395,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -369,10 +403,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -401,7 +435,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
+                <a:tint val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -414,13 +448,12 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
+                <a:tint val="80000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -440,2107 +473,2198 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="90" customWidth="1" min="3" max="3"/>
-    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="32.005" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
+    <col width="28.005" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
+    <col width="90.005" bestFit="1" customWidth="1" style="4" min="3" max="3"/>
+    <col width="88.005" bestFit="1" customWidth="1" style="4" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customFormat="1" customHeight="1" s="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Nombre exacto de la función</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Nombre de su clase</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Parámetros de entrada</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="38" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>input</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>IOProcessor</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>source_type: str, filepath_or_connection: str | Path, table_or_sheet: str | None = None, encoding: str = 'utf-8', delimiter: str = ','</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Lee datos desde CSV, Excel, Parquet o una tabla SQL y devuelve un DataFrame.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>output</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>IOProcessor</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, destination_type: str, output_path: str | Path, write_mode: str = 'overwrite', *, encoding: str = 'utf-8', delimiter: str = ','</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Guarda el DataFrame como CSV, Excel o Parquet; permite sobrescribir o anexar filas.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="4" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>read_csv</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>IOProcessor</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>filepath: str | Path</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Lee un archivo CSV; si falla la decodificación UTF-8, intenta con Latin-1.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="5" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>write_csv</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>IOProcessor</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, filepath: str | Path, index: bool = False</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Escribe el DataFrame en un archivo CSV y devuelve el mismo DataFrame.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="6" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>ConversionProcessor</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Convierte una columna a fecha y normaliza la hora a medianoche; puede reemplazar o crear columna.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="7" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>ConversionProcessor</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Convierte una columna a fecha y hora; puede reemplazar o crear columna.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="8" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>ConversionProcessor</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Convierte los valores de una columna a números decimales; puede reemplazar o crear columna.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="38" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="9" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>ConversionProcessor</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Convierte los valores de una columna a enteros; puede reemplazar o crear columna.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="38" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="10" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>str</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>ConversionProcessor</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Convierte los valores de una columna a texto; puede reemplazar o crear columna.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="38" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="11" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>make_date</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>ConversionProcessor</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column_day: str, column_month: str, column_year: str, replace: bool = False, new_column_name: str = 'date'</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Construye una fecha a partir de día, mes y año; ajusta días fuera del mes al último día válido.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="38" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="12" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>make_time</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>ConversionProcessor</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column_hour: str, column_minute: str, column_second: str, new_column_name: str = 'time'</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Construye valores de hora a partir de hora, minuto y segundo.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="38" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="13" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>make_date_time</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>ConversionProcessor</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column_date: str, column_hour: str, new_column_name: str = 'datetime'</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Combina una columna de fechas con otra de horas para producir valores datetime.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="14" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>date_parser</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>DateTimeProcessor</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, date_format: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Convierte una columna a fecha y hora usando el formato especificado.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="15" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>date_add</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>DateTimeProcessor</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, unit: str | None = None, amount: int | None = None, create_new_column: bool = False, new_column_name: str | None = None, *, part: str | None = None, interval: int | None = None, replace: bool | None = None</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Agrega un intervalo entero de días, semanas, meses, trimestres, años, horas, minutos o segundos a una fecha. Acepta unit/amount o part/interval y reemplazo opcional.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="38" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="16" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>date_sub</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>DateTimeProcessor</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, unit: str, amount: int, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Resta una cantidad de días, meses o años a una columna de fechas.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="38" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="17" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>date_diff</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>DateTimeProcessor</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, start_column: str, end_column: str, unit: str = 'days', create_new_column: bool = False, new_column_name: str | None = None, *, part: str | None = None</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Calcula la diferencia entre dos fechas en la unidad indicada: días, semanas, meses, trimestres, años, horas, minutos o segundos. Meses, trimestres y años cuentan unidades calendario completas.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="38" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="18" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>extract_date_part</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>DateTimeProcessor</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, part: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Extrae el año, mes, día o día de la semana de una columna de fechas.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="38" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="19" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>LogicalProcessor</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, sentencia1: str, sentencia2: str, reemplazar_campo: bool = True, nombre_nueva_columna: str | None = None</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Evalúa las sentencias 1 y 2 y devuelve su conjunción lógica AND como booleano. Reemplaza la columna fuente o crea una columna con el nombre indicado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>case</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>LogicalProcessor</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, sentencia1: str, sentencia2: str, reemplazar_campo: bool = True, nombre_nueva_columna: str | None = None</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Evalúa las sentencias 1 y 2 y devuelve su disyunción lógica OR como booleano. Reemplaza la columna fuente o crea una columna con el nombre indicado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>if</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>LogicalProcessor</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, sentencia1: str, sentencia2: str, reemplazar_campo: bool = True, nombre_nueva_columna: str | None = None</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Evalúa las sentencias 1 y 2 como una condición AND y devuelve el resultado booleano en la columna fuente o en una nueva columna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="31.5" customFormat="1" customHeight="1" s="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>elseif</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>LogicalProcessor</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, sentencia1: str, sentencia2: str, reemplazar_campo: bool = True, nombre_nueva_columna: str | None = None</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Combina las sentencias 1 y 2 como condiciones alternativas OR y devuelve el resultado booleano en la columna fuente o en una nueva columna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="31.5" customFormat="1" customHeight="1" s="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>or</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>LogicalProcessor</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, sentencia1: str, sentencia2: str, reemplazar_campo: bool = True, nombre_nueva_columna: str | None = None</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Evalúa las sentencias 1 y 2 y devuelve su disyunción lógica OR como booleano. Reemplaza la columna fuente o crea una columna con el nombre indicado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="31.5" customFormat="1" customHeight="1" s="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>not</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>LogicalProcessor</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, sentencia1: str, sentencia2: str | None = None, reemplazar_campo: bool = True, nombre_nueva_columna: str | None = None</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Niega la sentencia 1 y devuelve el resultado booleano. sentencia2 es opcional y no se utiliza. Reemplaza la columna fuente o crea una columna con el nombre indicado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="31.5" customFormat="1" customHeight="1" s="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>coalesce</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>LogicalProcessor</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>df: pd.DataFrame, column: str, default_value: object, create_new_column: bool = False, new_column_name: str | None = None</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Reemplaza valores nulos o cadenas vacías por un valor predeterminado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="38" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>(df: pandas.DataFrame, column: str, default_value: object, create_new_column: bool = False, new_column_name: str | None = None) -&gt; pandas.DataFrame</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Fill nulls and empty strings, without treating zero/False as missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="31.5" customFormat="1" customHeight="1" s="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>ifnull</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>LogicalProcessor</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>df: pd.DataFrame, column: str, default_value: object, create_new_column: bool = False, new_column_name: str | None = None</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Alias de coalesce: reemplaza valores nulos o cadenas vacías por un valor predeterminado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="38" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>(df: pandas.DataFrame, column: str, default_value: object, create_new_column: bool = False, new_column_name: str | None = None) -&gt; pandas.DataFrame</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Fill nulls and empty strings, without treating zero/False as missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="31.5" customFormat="1" customHeight="1" s="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>conditional_map</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>LogicalProcessor</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>df: pd.DataFrame, column: str, condition_func: Callable[[pd.Series], pd.Series] | Mapping[str, object], true_value: object, false_value: object, create_new_column: bool = False, new_column_name: str | None = None</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Evalúa una condición y asigna un valor verdadero o falso; admite callable o condición operador/valor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="38" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>and</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>LogicalProcessor</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>df: pd.DataFrame, *, operation: str = 'and', column: str, sentencia1: str, sentencia2: str | None = None, reemplazar_campo: bool = True, nombre_nueva_columna: str | None = None</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Evalúa dos condiciones sobre la columna y devuelve el AND booleano de ambas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="38" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>case</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>LogicalProcessor</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>df: pd.DataFrame, *, operation: str = 'case', column: str, sentencia1: str, sentencia2: str | None = None, reemplazar_campo: bool = True, nombre_nueva_columna: str | None = None</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Evalúa dos condiciones sobre la columna y devuelve el OR booleano de ambas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="38" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>if</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>LogicalProcessor</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>df: pd.DataFrame, *, operation: str = 'if', column: str, sentencia1: str, sentencia2: str | None = None, reemplazar_campo: bool = True, nombre_nueva_columna: str | None = None</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Evalúa dos condiciones sobre la columna y devuelve el AND booleano de ambas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="38" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>elseif</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>LogicalProcessor</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>df: pd.DataFrame, *, operation: str = 'elseif', column: str, sentencia1: str, sentencia2: str | None = None, reemplazar_campo: bool = True, nombre_nueva_columna: str | None = None</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Evalúa dos condiciones sobre la columna y devuelve el OR booleano de ambas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="38" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>or</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>LogicalProcessor</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>df: pd.DataFrame, *, operation: str = 'or', column: str, sentencia1: str, sentencia2: str | None = None, reemplazar_campo: bool = True, nombre_nueva_columna: str | None = None</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Evalúa dos condiciones sobre la columna y devuelve el OR booleano de ambas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="38" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>not</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>LogicalProcessor</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>df: pd.DataFrame, *, operation: str = 'not', column: str, sentencia1: str, sentencia2: str | None = None, reemplazar_campo: bool = True, nombre_nueva_columna: str | None = None</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Niega la condición indicada y devuelve su resultado booleano.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="38" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>(df: pandas.DataFrame, column: str, condition_func: collections.abc.Callable[[pandas.Series], pandas.Series] | collections.abc.Mapping[str, object], true_value: object, false_value: object, create_new_column: bool = False, new_column_name: str | None = None) -&gt; pandas.DataFrame</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Evaluate a Series callable or a JSON operator/value condition; never eval code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="31.5" customFormat="1" customHeight="1" s="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>absolute</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>NumericProcessor</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Calcula el valor absoluto de los valores de una columna.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="38" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="29" ht="31.5" customFormat="1" customHeight="1" s="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>abs</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>NumericProcessor</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Alias de absolute: calcula el valor absoluto de los valores de una columna.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="38" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="30" ht="31.5" customFormat="1" customHeight="1" s="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>arithmetic</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>NumericProcessor</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column_a: str, operator: str, column_b_or_value: str | float, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Aplica suma, resta, multiplicación o división entre una columna y otra columna o constante.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="38" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="31" ht="31.5" customFormat="1" customHeight="1" s="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>ceiling</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>NumericProcessor</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Redondea los valores de una columna hacia arriba al entero más cercano.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="38" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="32" ht="31.5" customFormat="1" customHeight="1" s="1">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>clean_float</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>NumericProcessor</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Convierte los valores a decimal; los valores nulos o no numéricos se reemplazan por cero.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="38" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="33" ht="31.5" customFormat="1" customHeight="1" s="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>floor</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>NumericProcessor</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Redondea los valores de una columna hacia abajo al entero más cercano.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="38" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="34" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>NumericProcessor</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column_a: str, column_b: str, new_column_name: str</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Crea una columna con el máximo fila a fila entre dos columnas numéricas.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="38" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="35" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>NumericProcessor</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column_a: str, column_b: str, new_column_name: str</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Crea una columna con el mínimo fila a fila entre dos columnas numéricas.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="38" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="36" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>power</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>NumericProcessor</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, value: float, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Eleva cada valor de una columna a la potencia indicada.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="38" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="37" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>round</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>NumericProcessor</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, decimals: int = 0, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Redondea los valores de una columna al número de decimales especificado.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="38" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="38" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>filter</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>RowProcessor</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, operator: str, value: object = None</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Filtra las filas según una comparación, búsqueda literal o comprobación de nulos.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="38" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="39" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>limit</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>RowProcessor</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, limit: int</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Devuelve como máximo la cantidad de filas indicada.</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="38" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="40" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>sample</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>RowProcessor</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, sample_type: str, fraction_or_count: float | int, random_state: int | None = None</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Selecciona las primeras filas o una muestra aleatoria por cantidad o fracción.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="38" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="41" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>union</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>StructuralProcessor</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>df_list: Sequence[pd.DataFrame], match_type: str = 'auto'</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Concatena dos o más DataFrames por nombre de columna o por posición.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="38" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="42" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>join</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>StructuralProcessor</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>left: pd.DataFrame, right: pd.DataFrame, how: str = 'inner', left_on: str | list[str] | None = None, right_on: str | list[str] | None = None, suffixes: Sequence[str] = ('_x', '_y')</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Combina dos DataFrames mediante claves de unión; puede inferir una clave compartida única.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="38" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="43" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>inner_join</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>StructuralProcessor</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>left: pd.DataFrame, right: pd.DataFrame, *, how: str = 'inner', left_on: str | list[str] | None = None, right_on: str | list[str] | None = None, suffixes: Sequence[str] = ('_x', '_y')</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Realiza una unión interna de dos DataFrames.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="38" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="44" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>outer_join</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>StructuralProcessor</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>left: pd.DataFrame, right: pd.DataFrame, *, how: str = 'outer', left_on: str | list[str] | None = None, right_on: str | list[str] | None = None, suffixes: Sequence[str] = ('_x', '_y')</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Realiza una unión externa de dos DataFrames.</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="38" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="45" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>add_column</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>StructuralProcessor</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column_name: str, value: object = None</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>Agrega una columna nueva con el valor constante indicado.</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="38" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="46" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>sort</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>StructuralProcessor</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, direction: str = 'asc'</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Ordena las filas por una columna en orden ascendente o descendente.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="38" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="47" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>drop-column</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>StructuralProcessor</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str | Sequence[str] | None = None, *, columns: Sequence[str] | None = None</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Elimina una o varias columnas del DataFrame.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="38" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="48" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>drop_column</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>StructuralProcessor</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str | Sequence[str] | None = None, *, columns: Sequence[str] | None = None</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Elimina una o varias columnas del DataFrame.</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="38" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="49" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>rename-column</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>StructuralProcessor</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, new_name: str</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>Renombra una columna existente.</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="38" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="50" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>rename_column</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>StructuralProcessor</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, new_name: str</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>Renombra una columna existente.</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="38" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="51" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>change-data-type</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>StructuralProcessor</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, new_type: str | None = None, *, target_type: str | None = None, create_new_column: bool | None = None, new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>Convierte una columna al tipo de dato especificado.</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="38" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="52" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>change_data_type</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>StructuralProcessor</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, new_type: str | None = None, *, target_type: str | None = None, create_new_column: bool | None = None, new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>Convierte una columna al tipo de dato especificado.</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="38" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="53" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>aggregate</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>StructuralProcessor</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, group_by: list[str], aggregations: dict[str, str | list[str]]</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>Agrupa filas y calcula las agregaciones solicitadas; conserva claves de agrupación nulas.</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="38" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="54" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>pivot</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>StructuralProcessor</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, pivot_type: str, index_cols: list[str], target_col: str, values_col: str</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>Reestructura datos entre formato columnas-a-filas y filas-a-columnas.</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="38" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="55" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>uppercase</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>TextProcessor</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>Convierte el texto de una columna a mayúsculas.</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="38" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="56" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>upper</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>TextProcessor</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>Alias de uppercase: convierte el texto de una columna a mayúsculas.</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="38" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="57" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>lowercase</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>TextProcessor</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>Convierte el texto de una columna a minúsculas.</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="38" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="58" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>lower</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>TextProcessor</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>Alias de lowercase: convierte el texto de una columna a minúsculas.</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="38" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="59" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>trim</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>TextProcessor</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None, *, side: str = 'both'</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>Elimina espacios en blanco al inicio, al final o en ambos lados del texto.</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="38" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="60" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>ltrim</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>TextProcessor</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>Elimina espacios en blanco al inicio del texto.</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="38" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="61" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>rtrim</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>TextProcessor</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>Elimina espacios en blanco al final del texto.</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="38" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="62" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>substring</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>TextProcessor</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, start: int, length: int, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>Extrae una subcadena usando posiciones de índice desde cero.</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="38" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="63" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>replace</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>TextProcessor</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, old_text: str, new_text: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>Reemplaza todas las apariciones literales de un texto por otro.</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="38" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="64" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>split</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>TextProcessor</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, delimiter: str, index: int | None = None, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>Divide texto por un delimitador; extrae un índice o expande las partes en columnas nuevas.</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="38" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="65" ht="38" customFormat="1" customHeight="1" s="1">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>concat</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>TextProcessor</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, columns: list[str], separator: str = '', create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>Concatena dos o más columnas de texto usando el separador indicado.</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="42" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="66" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>contains</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>TextProcessor</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, search_text: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>Devuelve True si el texto de cada celda contiene literalmente search_text; en caso contrario False. Los nulos producen False.</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="42" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="67" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>starts_with</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>TextProcessor</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, search_text: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>Devuelve True si el texto de cada celda comienza literalmente con search_text; en caso contrario False. Los nulos producen False.</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="42" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="68" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>ends_with</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>TextProcessor</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, search_text: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>Devuelve True si el texto de cada celda termina literalmente con search_text; en caso contrario False. Los nulos producen False.</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="42" customHeight="1">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="69" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>transform_left</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>TextProcessor</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, limit: int, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>Conserva como máximo los primeros limit caracteres de cada valor.</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="42" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="70" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>transform_right</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>TextProcessor</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, limit: int, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>Conserva como máximo los últimos limit caracteres de cada valor.</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="42" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="71" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>length</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>TextProcessor</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>Calcula la longitud en caracteres de cada celda; los valores nulos se mantienen nulos.</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="42" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="72" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>proper</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>TextProcessor</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>Convierte la primera letra de cada palabra a mayúscula y el resto a minúscula; puede reemplazar la columna o crear una nueva.</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="42" customHeight="1">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="73" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>propper</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>TextProcessor</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>Alias de proper: convierte la primera letra de cada palabra a mayúscula y el resto a minúscula; puede reemplazar la columna o crear una nueva.</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="42" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="74" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>date_parse</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, date_format: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>Convierte usando el formato indicado; los valores inválidos se convierten a NaT. Puede reemplazar o crear columna.</t>
         </is>
       </c>
-      <c r="D74" s="2" t="n"/>
-    </row>
-    <row r="75" ht="42" customHeight="1">
-      <c r="A75" s="2" t="inlineStr">
+    </row>
+    <row r="75" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>dateparse</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, date_format: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>Alias normalizado de date_parse; los valores inválidos se convierten a NaT.</t>
         </is>
       </c>
-      <c r="D75" s="2" t="n"/>
-    </row>
-    <row r="76" ht="42" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
+    </row>
+    <row r="76" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>date_trunc</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, part: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>Trunca la fecha al inicio de año, trimestre, mes, semana (lunes), día, hora, minuto o segundo.</t>
         </is>
       </c>
-      <c r="D76" s="2" t="n"/>
-    </row>
-    <row r="77" ht="42" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
+    </row>
+    <row r="77" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>datetrunc</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, part: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>Alias normalizado de date_trunc.</t>
         </is>
       </c>
-      <c r="D77" s="2" t="n"/>
-    </row>
-    <row r="78" ht="42" customHeight="1">
-      <c r="A78" s="2" t="inlineStr">
+    </row>
+    <row r="78" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>day</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>Extrae el día del mes como entero.</t>
         </is>
       </c>
-      <c r="D78" s="2" t="n"/>
-    </row>
-    <row r="79" ht="42" customHeight="1">
-      <c r="A79" s="2" t="inlineStr">
+    </row>
+    <row r="79" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>iso_quarter</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>Calcula el trimestre basado en semanas ISO; la semana 53 pertenece al trimestre 4.</t>
         </is>
       </c>
-      <c r="D79" s="2" t="n"/>
-    </row>
-    <row r="80" ht="42" customHeight="1">
-      <c r="A80" s="2" t="inlineStr">
+    </row>
+    <row r="80" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>isoquarter</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>Alias normalizado de iso_quarter.</t>
         </is>
       </c>
-      <c r="D80" s="2" t="n"/>
-    </row>
-    <row r="81" ht="42" customHeight="1">
-      <c r="A81" s="2" t="inlineStr">
+    </row>
+    <row r="81" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>iso_week</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>Extrae el número de semana ISO 8601 como entero.</t>
         </is>
       </c>
-      <c r="D81" s="2" t="n"/>
-    </row>
-    <row r="82" ht="42" customHeight="1">
-      <c r="A82" s="2" t="inlineStr">
+    </row>
+    <row r="82" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>isoweek</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>Alias normalizado de iso_week.</t>
         </is>
       </c>
-      <c r="D82" s="2" t="n"/>
-    </row>
-    <row r="83" ht="42" customHeight="1">
-      <c r="A83" s="2" t="inlineStr">
+    </row>
+    <row r="83" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>iso_week_day</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>Extrae el día de la semana ISO 8601: lunes=1 hasta domingo=7.</t>
         </is>
       </c>
-      <c r="D83" s="2" t="n"/>
-    </row>
-    <row r="84" ht="42" customHeight="1">
-      <c r="A84" s="2" t="inlineStr">
+    </row>
+    <row r="84" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>isoweekday</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>Alias normalizado de iso_week_day.</t>
         </is>
       </c>
-      <c r="D84" s="2" t="n"/>
-    </row>
-    <row r="85" ht="42" customHeight="1">
-      <c r="A85" s="2" t="inlineStr">
+    </row>
+    <row r="85" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>iso_year</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>Extrae el año ISO 8601, que puede diferir del año calendario.</t>
         </is>
       </c>
-      <c r="D85" s="2" t="n"/>
-    </row>
-    <row r="86" ht="42" customHeight="1">
-      <c r="A86" s="2" t="inlineStr">
+    </row>
+    <row r="86" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>isoyear</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t>Alias normalizado de iso_year.</t>
         </is>
       </c>
-      <c r="D86" s="2" t="n"/>
-    </row>
-    <row r="87" ht="42" customHeight="1">
-      <c r="A87" s="2" t="inlineStr">
+    </row>
+    <row r="87" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>now</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>Asigna la fecha y hora local actual del sistema a la columna destino.</t>
         </is>
       </c>
-      <c r="D87" s="2" t="n"/>
-    </row>
-    <row r="88" ht="42" customHeight="1">
-      <c r="A88" s="2" t="inlineStr">
+    </row>
+    <row r="88" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>quarter</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>Extrae el trimestre calendario como entero entre 1 y 4.</t>
         </is>
       </c>
-      <c r="D88" s="2" t="n"/>
-    </row>
-    <row r="89" ht="42" customHeight="1">
-      <c r="A89" s="2" t="inlineStr">
+    </row>
+    <row r="89" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>Asigna la fecha local actual del sistema sin hora a la columna destino.</t>
         </is>
       </c>
-      <c r="D89" s="2" t="n"/>
-    </row>
-    <row r="90" ht="42" customHeight="1">
-      <c r="A90" s="2" t="inlineStr">
+    </row>
+    <row r="90" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>week</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>Extrae el día de la semana como entero, lunes=0 hasta domingo=6.</t>
         </is>
       </c>
-      <c r="D90" s="2" t="n"/>
-    </row>
-    <row r="91" ht="42" customHeight="1">
-      <c r="A91" s="2" t="inlineStr">
+    </row>
+    <row r="91" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>Extrae el año calendario como entero.</t>
         </is>
       </c>
-      <c r="D91" s="2" t="n"/>
-    </row>
-    <row r="92" ht="42" customHeight="1">
-      <c r="A92" s="2" t="inlineStr">
+    </row>
+    <row r="92" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A92" s="3" t="inlineStr">
         <is>
           <t>dateadd</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, unit: str | None = None, amount: int | None = None, create_new_column: bool = False, new_column_name: str | None = None, *, part: str | None = None, interval: int | None = None, replace: bool | None = None</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>Alias normalizado de date_add.</t>
         </is>
       </c>
-      <c r="D92" s="2" t="n"/>
-    </row>
-    <row r="93" ht="42" customHeight="1">
-      <c r="A93" s="2" t="inlineStr">
+    </row>
+    <row r="93" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t>datediff</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, start_column: str, end_column: str, unit: str = 'days', create_new_column: bool = False, new_column_name: str | None = None, *, part: str | None = None</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t>Alias normalizado de date_diff.</t>
         </is>
       </c>
-      <c r="D93" s="2" t="n"/>
-    </row>
-    <row r="94" ht="42" customHeight="1">
-      <c r="A94" s="2" t="inlineStr">
+    </row>
+    <row r="94" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>date_name</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, part: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t>Devuelve el nombre en español del mes o del día de semana; año y trimestre se devuelven como texto.</t>
         </is>
       </c>
-      <c r="D94" s="2" t="n"/>
-    </row>
-    <row r="95" ht="42" customHeight="1">
-      <c r="A95" s="2" t="inlineStr">
+    </row>
+    <row r="95" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>datename</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, part: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="D95" s="3" t="inlineStr">
         <is>
           <t>Alias normalizado de date_name.</t>
         </is>
       </c>
-      <c r="D95" s="2" t="n"/>
-    </row>
-    <row r="96" ht="42" customHeight="1">
-      <c r="A96" s="2" t="inlineStr">
+    </row>
+    <row r="96" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>Extrae el número del mes como entero entre 1 y 12.</t>
         </is>
       </c>
-      <c r="D96" s="2" t="n"/>
-    </row>
-    <row r="97" ht="42" customHeight="1">
-      <c r="A97" s="2" t="inlineStr">
+    </row>
+    <row r="97" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>date add</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>DateTimeProcessor</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, unit: str | None = None, amount: int | None = None, create_new_column: bool = False, new_column_name: str | None = None, *, part: str | None = None, interval: int | None = None, replace: bool | None = None</t>
         </is>
       </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t>Alias textual de date_add.</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="42" customHeight="1">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="98" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t>date diff</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>DateTimeProcessor</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, start_column: str, end_column: str, unit: str = 'days', create_new_column: bool = False, new_column_name: str | None = None, *, part: str | None = None</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t>Alias textual de date_diff.</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="42" customHeight="1">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="99" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t>date name</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>DateTimeProcessor</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column: str, part: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t>Alias textual de date_name.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D99"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>

--- a/catalogo_operaciones.xlsx
+++ b/catalogo_operaciones.xlsx
@@ -8,7 +8,9 @@
   <sheets>
     <sheet name="Operaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Operaciones'!$A$1:$D$100</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -175,7 +177,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OperationsCatalog" displayName="OperationsCatalog" ref="A1:D99" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OperationsCatalog" displayName="OperationsCatalog" ref="A1:D100" headerRowCount="1" totalsRowShown="0">
   <autoFilter ref="A1:D99"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Nombre exacto de la función"/>
@@ -476,7 +478,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32.005" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
@@ -1884,7 +1886,7 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, delimiter: str, index: int | None = None, create_new_column: bool = False, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, delimiter: str, index: int | None = None, create_new_column: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -1896,7 +1898,7 @@
     <row r="65" ht="38" customFormat="1" customHeight="1" s="1">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>concat</t>
+          <t>concat_column</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -1906,12 +1908,12 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, columns: list[str], separator: str = '', create_new_column: bool = False, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, columns: list[str], separator: str = '', create_new_column: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Concatena dos o más columnas de texto usando el separador indicado.</t>
+          <t>Concatena dos o más columnas de texto y crea por defecto una columna nueva; los valores nulos de las columnas de entrada se propagan al resultado.</t>
         </is>
       </c>
     </row>
@@ -1928,7 +1930,7 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, search_text: str, create_new_column: bool = False, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, search_text: str, create_new_column: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -1950,7 +1952,7 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, search_text: str, create_new_column: bool = False, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, search_text: str, create_new_column: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -1972,7 +1974,7 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, search_text: str, create_new_column: bool = False, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, search_text: str, create_new_column: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -2038,7 +2040,7 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -2663,7 +2665,30 @@
         </is>
       </c>
     </row>
+    <row r="100" ht="42" customHeight="1">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>concat_text</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>TextProcessor</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column_name: str, value: str, create_new_column: bool = False, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>Concatena un texto literal al contenido de la columna y reemplaza por defecto su valor; puede crear una columna nueva si se solicita.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:D100"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/catalogo_operaciones.xlsx
+++ b/catalogo_operaciones.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Operaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Operaciones'!$A$1:$D$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Operaciones'!$A$1:$D$102</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -177,7 +177,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OperationsCatalog" displayName="OperationsCatalog" ref="A1:D100" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OperationsCatalog" displayName="OperationsCatalog" ref="A1:D102" headerRowCount="1" totalsRowShown="0">
   <autoFilter ref="A1:D99"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Nombre exacto de la función"/>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:D102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32.005" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="38" customFormat="1" customHeight="1" s="1">
+    <row r="45" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>add_column</t>
+          <t>left_join</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1468,19 +1468,19 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column_name: str, value: object = None</t>
+          <t>left: pd.DataFrame, right: pd.DataFrame, *, how: str = 'left', left_on: str | list[str] | None = None, right_on: str | list[str] | None = None, suffixes: Sequence[str] = ('_x', '_y')</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Agrega una columna nueva con el valor constante indicado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="38" customFormat="1" customHeight="1" s="1">
+          <t>Realiza una unión left entre dos DataFrames; conserva todas las filas del DataFrame izquierdo y las coincidencias del derecho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>sort</t>
+          <t>right_join</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1490,19 +1490,19 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, direction: str = 'asc'</t>
+          <t>left: pd.DataFrame, right: pd.DataFrame, *, how: str = 'right', left_on: str | list[str] | None = None, right_on: str | list[str] | None = None, suffixes: Sequence[str] = ('_x', '_y')</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Ordena las filas por una columna en orden ascendente o descendente.</t>
+          <t>Realiza una unión right entre dos DataFrames; conserva todas las filas del DataFrame derecho y las coincidencias del izquierdo.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="38" customFormat="1" customHeight="1" s="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>drop-column</t>
+          <t>add_column</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1512,41 +1512,41 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str | Sequence[str] | None = None, *, columns: Sequence[str] | None = None</t>
+          <t>df: pd.DataFrame, column_name: str, value: object = None</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Elimina una o varias columnas del DataFrame.</t>
+          <t>Agrega una columna nueva con el valor constante indicado.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="38" customFormat="1" customHeight="1" s="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>drop_column</t>
+          <t>sort</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>StructuralProcessor</t>
+          <t>RowProcessor</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str | Sequence[str] | None = None, *, columns: Sequence[str] | None = None</t>
+          <t>df: pd.DataFrame, column: str, direction: str = 'asc'</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Elimina una o varias columnas del DataFrame.</t>
+          <t>Ordena las filas por una columna en orden ascendente o descendente.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="38" customFormat="1" customHeight="1" s="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>rename-column</t>
+          <t>drop-column</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1556,19 +1556,19 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, new_name: str</t>
+          <t>df: pd.DataFrame, column: str | Sequence[str] | None = None, *, columns: Sequence[str] | None = None</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Renombra una columna existente.</t>
+          <t>Elimina una o varias columnas del DataFrame.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="38" customFormat="1" customHeight="1" s="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>rename_column</t>
+          <t>drop_column</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -1578,19 +1578,19 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, new_name: str</t>
+          <t>df: pd.DataFrame, column: str | Sequence[str] | None = None, *, columns: Sequence[str] | None = None</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Renombra una columna existente.</t>
+          <t>Elimina una o varias columnas del DataFrame.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="38" customFormat="1" customHeight="1" s="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>change-data-type</t>
+          <t>rename-column</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1600,19 +1600,19 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, new_type: str | None = None, *, target_type: str | None = None, create_new_column: bool | None = None, new_column: bool = False, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, new_name: str</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Convierte una columna al tipo de dato especificado.</t>
+          <t>Renombra una columna existente.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="38" customFormat="1" customHeight="1" s="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>change_data_type</t>
+          <t>rename_column</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -1622,19 +1622,19 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, new_type: str | None = None, *, target_type: str | None = None, create_new_column: bool | None = None, new_column: bool = False, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, new_name: str</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Convierte una columna al tipo de dato especificado.</t>
+          <t>Renombra una columna existente.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="38" customFormat="1" customHeight="1" s="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>aggregate</t>
+          <t>change-data-type</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -1644,19 +1644,19 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, group_by: list[str], aggregations: dict[str, str | list[str]]</t>
+          <t>df: pd.DataFrame, column: str, new_type: str | None = None, *, target_type: str | None = None, create_new_column: bool | None = None, new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Agrupa filas y calcula las agregaciones solicitadas; conserva claves de agrupación nulas.</t>
+          <t>Convierte una columna al tipo de dato especificado.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="38" customFormat="1" customHeight="1" s="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>pivot</t>
+          <t>change_data_type</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -1666,63 +1666,63 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, pivot_type: str, index_cols: list[str], target_col: str, values_col: str</t>
+          <t>df: pd.DataFrame, column: str, new_type: str | None = None, *, target_type: str | None = None, create_new_column: bool | None = None, new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Reestructura datos entre formato columnas-a-filas y filas-a-columnas.</t>
+          <t>Convierte una columna al tipo de dato especificado.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="38" customFormat="1" customHeight="1" s="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>uppercase</t>
+          <t>aggregate</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>TextProcessor</t>
+          <t>StructuralProcessor</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
+          <t>df: pd.DataFrame, group_by: list[str], aggregations: dict[str, str | list[str]]</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Convierte el texto de una columna a mayúsculas.</t>
+          <t>Agrupa filas y calcula las agregaciones solicitadas; conserva claves de agrupación nulas.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="38" customFormat="1" customHeight="1" s="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>upper</t>
+          <t>pivot</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>TextProcessor</t>
+          <t>StructuralProcessor</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
+          <t>df: pd.DataFrame, pivot_type: str, index_cols: list[str], target_col: str, values_col: str</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Alias de uppercase: convierte el texto de una columna a mayúsculas.</t>
+          <t>Reestructura datos entre formato columnas-a-filas y filas-a-columnas.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="38" customFormat="1" customHeight="1" s="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>lowercase</t>
+          <t>uppercase</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -1737,14 +1737,14 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Convierte el texto de una columna a minúsculas.</t>
+          <t>Convierte el texto de una columna a mayúsculas.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="38" customFormat="1" customHeight="1" s="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>lower</t>
+          <t>upper</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -1759,14 +1759,14 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Alias de lowercase: convierte el texto de una columna a minúsculas.</t>
+          <t>Alias de uppercase: convierte el texto de una columna a mayúsculas.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="38" customFormat="1" customHeight="1" s="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>trim</t>
+          <t>lowercase</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -1776,19 +1776,19 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None, *, side: str = 'both'</t>
+          <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Elimina espacios en blanco al inicio, al final o en ambos lados del texto.</t>
+          <t>Convierte el texto de una columna a minúsculas.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="38" customFormat="1" customHeight="1" s="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>ltrim</t>
+          <t>lower</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -1798,19 +1798,19 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Elimina espacios en blanco al inicio del texto.</t>
+          <t>Alias de lowercase: convierte el texto de una columna a minúsculas.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="38" customFormat="1" customHeight="1" s="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>rtrim</t>
+          <t>trim</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -1820,19 +1820,19 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None, *, side: str = 'both'</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Elimina espacios en blanco al final del texto.</t>
+          <t>Elimina espacios en blanco al inicio, al final o en ambos lados del texto.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="38" customFormat="1" customHeight="1" s="1">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>substring</t>
+          <t>ltrim</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -1842,19 +1842,19 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, start: int, length: int, create_new_column: bool = False, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Extrae una subcadena usando posiciones de índice desde cero.</t>
+          <t>Elimina espacios en blanco al inicio del texto.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="38" customFormat="1" customHeight="1" s="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>replace</t>
+          <t>rtrim</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -1864,19 +1864,19 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, old_text: str, new_text: str, create_new_column: bool = False, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Reemplaza todas las apariciones literales de un texto por otro.</t>
+          <t>Elimina espacios en blanco al final del texto.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="38" customFormat="1" customHeight="1" s="1">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>split</t>
+          <t>substring</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -1886,19 +1886,19 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, delimiter: str, index: int | None = None, create_new_column: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, start: int, length: int, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Divide texto por un delimitador; extrae un índice o expande las partes en columnas nuevas.</t>
+          <t>Extrae una subcadena usando posiciones de índice desde cero.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="38" customFormat="1" customHeight="1" s="1">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>concat_column</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -1908,19 +1908,19 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, columns: list[str], separator: str = '', create_new_column: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, old_text: str, new_text: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Concatena dos o más columnas de texto y crea por defecto una columna nueva; los valores nulos de las columnas de entrada se propagan al resultado.</t>
+          <t>Reemplaza todas las apariciones literales de un texto por otro.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>contains</t>
+          <t>split</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -1930,19 +1930,19 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, search_text: str, create_new_column: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, delimiter: str, index: int | None = None, create_new_column: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Devuelve True si el texto de cada celda contiene literalmente search_text; en caso contrario False. Los nulos producen False.</t>
+          <t>Divide texto por un delimitador; extrae un índice o expande las partes en columnas nuevas.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>starts_with</t>
+          <t>concat_column</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -1952,19 +1952,19 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, search_text: str, create_new_column: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, columns: list[str], separator: str = '', create_new_column: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Devuelve True si el texto de cada celda comienza literalmente con search_text; en caso contrario False. Los nulos producen False.</t>
+          <t>Concatena dos o más columnas de texto y crea por defecto una columna nueva; los valores nulos de las columnas de entrada se propagan al resultado.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>ends_with</t>
+          <t>contains</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -1979,14 +1979,14 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Devuelve True si el texto de cada celda termina literalmente con search_text; en caso contrario False. Los nulos producen False.</t>
+          <t>Devuelve True si el texto de cada celda contiene literalmente search_text; en caso contrario False. Los nulos producen False.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>transform_left</t>
+          <t>starts_with</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -1996,19 +1996,19 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, limit: int, create_new_column: bool = False, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, search_text: str, create_new_column: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Conserva como máximo los primeros limit caracteres de cada valor.</t>
+          <t>Devuelve True si el texto de cada celda comienza literalmente con search_text; en caso contrario False. Los nulos producen False.</t>
         </is>
       </c>
     </row>
     <row r="70" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>transform_right</t>
+          <t>ends_with</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2018,19 +2018,19 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, limit: int, create_new_column: bool = False, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, search_text: str, create_new_column: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Conserva como máximo los últimos limit caracteres de cada valor.</t>
+          <t>Devuelve True si el texto de cada celda termina literalmente con search_text; en caso contrario False. Los nulos producen False.</t>
         </is>
       </c>
     </row>
     <row r="71" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>length</t>
+          <t>transform_left</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2040,19 +2040,19 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, create_new_column: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, limit: int, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Calcula la longitud en caracteres de cada celda; los valores nulos se mantienen nulos.</t>
+          <t>Conserva como máximo los primeros limit caracteres de cada valor.</t>
         </is>
       </c>
     </row>
     <row r="72" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>proper</t>
+          <t>transform_right</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2062,19 +2062,19 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
+          <t>df: pd.DataFrame, column: str, limit: int, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Convierte la primera letra de cada palabra a mayúscula y el resto a minúscula; puede reemplazar la columna o crear una nueva.</t>
+          <t>Conserva como máximo los últimos limit caracteres de cada valor.</t>
         </is>
       </c>
     </row>
     <row r="73" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>propper</t>
+          <t>length</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2084,63 +2084,63 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Alias de proper: convierte la primera letra de cada palabra a mayúscula y el resto a minúscula; puede reemplazar la columna o crear una nueva.</t>
+          <t>Calcula la longitud en caracteres de cada celda; los valores nulos se mantienen nulos.</t>
         </is>
       </c>
     </row>
     <row r="74" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>date_parse</t>
+          <t>proper</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>DateTimeProcessor</t>
+          <t>TextProcessor</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, date_format: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Convierte usando el formato indicado; los valores inválidos se convierten a NaT. Puede reemplazar o crear columna.</t>
+          <t>Convierte la primera letra de cada palabra a mayúscula y el resto a minúscula; puede reemplazar la columna o crear una nueva.</t>
         </is>
       </c>
     </row>
     <row r="75" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>dateparse</t>
+          <t>propper</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>DateTimeProcessor</t>
+          <t>TextProcessor</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, date_format: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Alias normalizado de date_parse; los valores inválidos se convierten a NaT.</t>
+          <t>Alias de proper: convierte la primera letra de cada palabra a mayúscula y el resto a minúscula; puede reemplazar la columna o crear una nueva.</t>
         </is>
       </c>
     </row>
     <row r="76" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>date_trunc</t>
+          <t>date_parse</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2150,19 +2150,19 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, part: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, date_format: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Trunca la fecha al inicio de año, trimestre, mes, semana (lunes), día, hora, minuto o segundo.</t>
+          <t>Convierte usando el formato indicado; los valores inválidos se convierten a NaT. Puede reemplazar o crear columna.</t>
         </is>
       </c>
     </row>
     <row r="77" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>datetrunc</t>
+          <t>dateparse</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2172,19 +2172,19 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, part: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, date_format: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Alias normalizado de date_trunc.</t>
+          <t>Alias normalizado de date_parse; los valores inválidos se convierten a NaT.</t>
         </is>
       </c>
     </row>
     <row r="78" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>day</t>
+          <t>date_trunc</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2194,19 +2194,19 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, part: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Extrae el día del mes como entero.</t>
+          <t>Trunca la fecha al inicio de año, trimestre, mes, semana (lunes), día, hora, minuto o segundo.</t>
         </is>
       </c>
     </row>
     <row r="79" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>iso_quarter</t>
+          <t>datetrunc</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2216,19 +2216,19 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, part: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Calcula el trimestre basado en semanas ISO; la semana 53 pertenece al trimestre 4.</t>
+          <t>Alias normalizado de date_trunc.</t>
         </is>
       </c>
     </row>
     <row r="80" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>isoquarter</t>
+          <t>day</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2243,14 +2243,14 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Alias normalizado de iso_quarter.</t>
+          <t>Extrae el día del mes como entero.</t>
         </is>
       </c>
     </row>
     <row r="81" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>iso_week</t>
+          <t>iso_quarter</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2265,14 +2265,14 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Extrae el número de semana ISO 8601 como entero.</t>
+          <t>Calcula el trimestre basado en semanas ISO; la semana 53 pertenece al trimestre 4.</t>
         </is>
       </c>
     </row>
     <row r="82" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>isoweek</t>
+          <t>isoquarter</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -2287,14 +2287,14 @@
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Alias normalizado de iso_week.</t>
+          <t>Alias normalizado de iso_quarter.</t>
         </is>
       </c>
     </row>
     <row r="83" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>iso_week_day</t>
+          <t>iso_week</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2309,14 +2309,14 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Extrae el día de la semana ISO 8601: lunes=1 hasta domingo=7.</t>
+          <t>Extrae el número de semana ISO 8601 como entero.</t>
         </is>
       </c>
     </row>
     <row r="84" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>isoweekday</t>
+          <t>isoweek</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -2331,14 +2331,14 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Alias normalizado de iso_week_day.</t>
+          <t>Alias normalizado de iso_week.</t>
         </is>
       </c>
     </row>
     <row r="85" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>iso_year</t>
+          <t>iso_week_day</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -2353,14 +2353,14 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Extrae el año ISO 8601, que puede diferir del año calendario.</t>
+          <t>Extrae el día de la semana ISO 8601: lunes=1 hasta domingo=7.</t>
         </is>
       </c>
     </row>
     <row r="86" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>isoyear</t>
+          <t>isoweekday</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -2375,14 +2375,14 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Alias normalizado de iso_year.</t>
+          <t>Alias normalizado de iso_week_day.</t>
         </is>
       </c>
     </row>
     <row r="87" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>now</t>
+          <t>iso_year</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -2397,14 +2397,14 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Asigna la fecha y hora local actual del sistema a la columna destino.</t>
+          <t>Extrae el año ISO 8601, que puede diferir del año calendario.</t>
         </is>
       </c>
     </row>
     <row r="88" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>quarter</t>
+          <t>isoyear</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -2419,14 +2419,14 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Extrae el trimestre calendario como entero entre 1 y 4.</t>
+          <t>Alias normalizado de iso_year.</t>
         </is>
       </c>
     </row>
     <row r="89" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>today</t>
+          <t>now</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -2441,14 +2441,14 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Asigna la fecha local actual del sistema sin hora a la columna destino.</t>
+          <t>Asigna la fecha y hora local actual del sistema a la columna destino.</t>
         </is>
       </c>
     </row>
     <row r="90" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>week</t>
+          <t>quarter</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -2463,14 +2463,14 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Extrae el día de la semana como entero, lunes=0 hasta domingo=6.</t>
+          <t>Extrae el trimestre calendario como entero entre 1 y 4.</t>
         </is>
       </c>
     </row>
     <row r="91" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>today</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -2485,14 +2485,14 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Extrae el año calendario como entero.</t>
+          <t>Asigna la fecha local actual del sistema sin hora a la columna destino.</t>
         </is>
       </c>
     </row>
     <row r="92" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>dateadd</t>
+          <t>week</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -2502,19 +2502,19 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, unit: str | None = None, amount: int | None = None, create_new_column: bool = False, new_column_name: str | None = None, *, part: str | None = None, interval: int | None = None, replace: bool | None = None</t>
+          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Alias normalizado de date_add.</t>
+          <t>Extrae el día de la semana como entero, lunes=0 hasta domingo=6.</t>
         </is>
       </c>
     </row>
     <row r="93" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>datediff</t>
+          <t>year</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -2524,19 +2524,19 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, start_column: str, end_column: str, unit: str = 'days', create_new_column: bool = False, new_column_name: str | None = None, *, part: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Alias normalizado de date_diff.</t>
+          <t>Extrae el año calendario como entero.</t>
         </is>
       </c>
     </row>
     <row r="94" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>date_name</t>
+          <t>dateadd</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -2546,19 +2546,19 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, part: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, unit: str | None = None, amount: int | None = None, create_new_column: bool = False, new_column_name: str | None = None, *, part: str | None = None, interval: int | None = None, replace: bool | None = None</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Devuelve el nombre en español del mes o del día de semana; año y trimestre se devuelven como texto.</t>
+          <t>Alias normalizado de date_add.</t>
         </is>
       </c>
     </row>
     <row r="95" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>datename</t>
+          <t>datediff</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -2568,19 +2568,19 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, part: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, start_column: str, end_column: str, unit: str = 'days', create_new_column: bool = False, new_column_name: str | None = None, *, part: str | None = None</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Alias normalizado de date_name.</t>
+          <t>Alias normalizado de date_diff.</t>
         </is>
       </c>
     </row>
     <row r="96" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>date_name</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -2590,19 +2590,19 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, part: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Extrae el número del mes como entero entre 1 y 12.</t>
+          <t>Devuelve el nombre en español del mes o del día de semana; año y trimestre se devuelven como texto.</t>
         </is>
       </c>
     </row>
     <row r="97" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>date add</t>
+          <t>datename</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -2612,19 +2612,19 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, unit: str | None = None, amount: int | None = None, create_new_column: bool = False, new_column_name: str | None = None, *, part: str | None = None, interval: int | None = None, replace: bool | None = None</t>
+          <t>df: pd.DataFrame, column: str, part: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Alias textual de date_add.</t>
+          <t>Alias normalizado de date_name.</t>
         </is>
       </c>
     </row>
     <row r="98" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>date diff</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -2634,19 +2634,19 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, start_column: str, end_column: str, unit: str = 'days', create_new_column: bool = False, new_column_name: str | None = None, *, part: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Alias textual de date_diff.</t>
+          <t>Extrae el número del mes como entero entre 1 y 12.</t>
         </is>
       </c>
     </row>
     <row r="99" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>date name</t>
+          <t>date add</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -2656,39 +2656,83 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, part: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, unit: str | None = None, amount: int | None = None, create_new_column: bool = False, new_column_name: str | None = None, *, part: str | None = None, interval: int | None = None, replace: bool | None = None</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Alias textual de date_name.</t>
+          <t>Alias textual de date_add.</t>
         </is>
       </c>
     </row>
     <row r="100" ht="42" customHeight="1">
       <c r="A100" s="3" t="inlineStr">
         <is>
+          <t>date diff</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, start_column: str, end_column: str, unit: str = 'days', create_new_column: bool = False, new_column_name: str | None = None, *, part: str | None = None</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>Alias textual de date_diff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>date name</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>DateTimeProcessor</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>df: pd.DataFrame, column: str, part: str, replace: bool = True, new_column_name: str | None = None</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>Alias textual de date_name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
           <t>concat_text</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
+      <c r="B102" s="3" t="inlineStr">
         <is>
           <t>TextProcessor</t>
         </is>
       </c>
-      <c r="C100" s="3" t="inlineStr">
+      <c r="C102" s="3" t="inlineStr">
         <is>
           <t>df: pd.DataFrame, column_name: str, value: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
-      <c r="D100" s="3" t="inlineStr">
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>Concatena un texto literal al contenido de la columna y reemplaza por defecto su valor; puede crear una columna nueva si se solicita.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D100"/>
+  <autoFilter ref="A1:D102"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/catalogo_operaciones.xlsx
+++ b/catalogo_operaciones.xlsx
@@ -610,7 +610,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column_day: str, column_month: str, column_year: str, replace: bool = False, new_column_name: str = 'date'</t>
+          <t>df: pd.DataFrame, column_day: str, column_month: str, column_year: str, create_new_column: bool = True, new_column_name: str = 'date'</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, unit: str | None = None, amount: int | None = None, create_new_column: bool = False, new_column_name: str | None = None, *, part: str | None = None, interval: int | None = None, replace: bool | None = None</t>
+          <t>df: pd.DataFrame, column: str, unit: str | None = None, amount: int | None = None, create_new_column: bool = False, new_column_name: str | None = None, *, part: str | None = None, interval: int | None = None</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Agrega un intervalo entero de días, semanas, meses, trimestres, años, horas, minutos o segundos a una fecha. Acepta unit/amount o part/interval y reemplazo opcional.</t>
+          <t>Agrega un intervalo entero de días, semanas, meses, trimestres, años, horas, minutos o segundos a una fecha. Acepta unit/amount o part/interval y creación de columna opcional mediante create_new_column.</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, value: float, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
+          <t>df: pd.DataFrame, column: str, value: float, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, decimals: int = 0, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
+          <t>df: pd.DataFrame, column: str, decimals: int = 0, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, new_type: str | None = None, *, target_type: str | None = None, create_new_column: bool | None = None, new_column: bool = False, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, new_type: str | None = None, *, target_type: str | None = None, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, new_type: str | None = None, *, target_type: str | None = None, create_new_column: bool | None = None, new_column: bool = False, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, new_type: str | None = None, *, target_type: str | None = None, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, new_column: bool = False, new_column_name: str | None = None, *, create_new_column: bool | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, date_format: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, date_format: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Convierte usando el formato indicado; los valores inválidos se convierten a NaT. Puede reemplazar o crear columna.</t>
+          <t>Convierte usando el formato indicado; los valores inválidos se convierten a NaT. Puede sobrescribir la columna fuente o crear una nueva con create_new_column.</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, date_format: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, date_format: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, part: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, part: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, part: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, part: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, unit: str | None = None, amount: int | None = None, create_new_column: bool = False, new_column_name: str | None = None, *, part: str | None = None, interval: int | None = None, replace: bool | None = None</t>
+          <t>df: pd.DataFrame, column: str, unit: str | None = None, amount: int | None = None, create_new_column: bool = False, new_column_name: str | None = None, *, part: str | None = None, interval: int | None = None</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, part: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, part: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, part: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, part: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, unit: str | None = None, amount: int | None = None, create_new_column: bool = False, new_column_name: str | None = None, *, part: str | None = None, interval: int | None = None, replace: bool | None = None</t>
+          <t>df: pd.DataFrame, column: str, unit: str | None = None, amount: int | None = None, create_new_column: bool = False, new_column_name: str | None = None, *, part: str | None = None, interval: int | None = None</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>df: pd.DataFrame, column: str, part: str, replace: bool = True, new_column_name: str | None = None</t>
+          <t>df: pd.DataFrame, column: str, part: str, create_new_column: bool = False, new_column_name: str | None = None</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
